--- a/apps/api/tests/regression/regression_farms.xlsx
+++ b/apps/api/tests/regression/regression_farms.xlsx
@@ -714,7 +714,11 @@
           <t>https://www.drive.google.com</t>
         </is>
       </c>
-      <c r="S3" s="10" t="n"/>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>https://www.drive.google.com/</t>
+        </is>
+      </c>
       <c r="T3" s="10" t="n"/>
       <c r="U3" s="10" t="n"/>
       <c r="V3" s="10" t="n"/>
@@ -20127,7 +20131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20476,7 +20480,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>NOT_VALID</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20616,27 +20620,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.00 %</t>
+          <t>sin datos</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.00 %</t>
+          <t>sin datos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.00 %</t>
+          <t>sin datos</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.00 %</t>
+          <t>sin datos</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.00 %</t>
+          <t>sin datos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -20665,22 +20669,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8.02 % (MEDIUM)</t>
+          <t>61.26 % (MEDIUM)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>overlap</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>F06, F07</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>100.00 % (HIGH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>invalid_geometry</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>F10</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Self-intersection[-76.35 -0.25]</t>
         </is>

--- a/apps/api/tests/regression/regression_farms.xlsx
+++ b/apps/api/tests/regression/regression_farms.xlsx
@@ -20215,12 +20215,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>80.51 %</t>
+          <t>59.15 %</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>52.33 %</t>
+          <t>37.27 %</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>60.38 %</t>
+          <t>46.19 %</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -20260,12 +20260,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32.27 %</t>
+          <t>23.84 %</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.20 %</t>
+          <t>9.62 %</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -20350,12 +20350,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>93.03 %</t>
+          <t>69.72 %</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>100.00 %</t>
+          <t>76.78 %</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18.40 %</t>
+          <t>14.30 %</t>
         </is>
       </c>
     </row>
@@ -20530,27 +20530,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.50 %</t>
+          <t>8.68 %</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.17 %</t>
+          <t>6.19 %</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.83 %</t>
+          <t>2.82 %</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9.00 %</t>
+          <t>8.36 %</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.33 %</t>
+          <t>0.22 %</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
